--- a/Document/Boost/Boost.xlsx
+++ b/Document/Boost/Boost.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\Boost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDC2AEF-EF75-4230-918F-5EFEA2306AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046010BD-1518-4123-B068-6DF65F07E459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="matlab reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -73,15 +74,29 @@
   <si>
     <t>IM2(M2ON)</t>
   </si>
+  <si>
+    <t>Simulink仿真----升压(Boost)变换器_simulink升压变压器模块怎么找-CSDN博客</t>
+  </si>
+  <si>
+    <t>手把手教你Boost升压电路的Simulink仿真（含开环，闭环，双闭环控制，PI参数调节方法）_哔哩哔哩_bilibili</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -214,22 +229,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -267,13 +274,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -283,11 +289,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3943,766 +3957,762 @@
       <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="K30" s="16"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="5"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="K31" s="18" t="s">
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="K31" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="19"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="10"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="7"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="7"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="K32" s="15"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="4"/>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="13"/>
-      <c r="U33" s="5"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="K33" s="15"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="2"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="K34" s="18" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="K34" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="L34" s="19"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="7"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="12"/>
+      <c r="U34" s="4"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="23"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="18"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="K36" s="13" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="K36" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="L36" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="5"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+      <c r="V36" s="11"/>
+      <c r="W36" s="2"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K37" s="15"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="7"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="4"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K38" s="15"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="7"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="4"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K39" s="15"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="7"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="4"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K40" s="15"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="7"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="4"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K41" s="15"/>
-      <c r="L41" s="20" t="s">
+      <c r="K41" s="12"/>
+      <c r="L41" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="7"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="4"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K42" s="15"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="7"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="4"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K43" s="15"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="7"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="4"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K44" s="15"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="7"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="4"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K45" s="15"/>
-      <c r="L45" s="20" t="s">
+      <c r="K45" s="12"/>
+      <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="7"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="4"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K46" s="15"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="20"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="7"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="4"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K47" s="9"/>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
-      <c r="S47" s="12"/>
-      <c r="T47" s="12"/>
-      <c r="U47" s="12"/>
-      <c r="V47" s="12"/>
-      <c r="W47" s="10"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="7"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="5"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="11"/>
+      <c r="W48" s="2"/>
     </row>
     <row r="49" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K49" s="15"/>
-      <c r="L49" s="6" t="s">
+      <c r="K49" s="12"/>
+      <c r="L49" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="7"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="4"/>
     </row>
     <row r="50" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K50" s="15"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="7"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="4"/>
     </row>
     <row r="51" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K51" s="15"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="7"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="4"/>
     </row>
     <row r="52" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K52" s="15"/>
-      <c r="L52" s="6" t="s">
+      <c r="K52" s="12"/>
+      <c r="L52" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="7"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="4"/>
     </row>
     <row r="53" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K53" s="15"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="7"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="4"/>
     </row>
     <row r="54" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K54" s="15"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="7"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="4"/>
     </row>
     <row r="55" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K55" s="15"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="7"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="4"/>
     </row>
     <row r="56" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K56" s="15"/>
-      <c r="L56" s="6" t="s">
+      <c r="K56" s="12"/>
+      <c r="L56" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="7"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="4"/>
     </row>
     <row r="57" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K57" s="9"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="12"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="12"/>
-      <c r="W57" s="10"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="7"/>
     </row>
     <row r="58" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K58" s="27"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="7"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="4"/>
     </row>
     <row r="59" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K59" s="13"/>
-      <c r="L59" s="14" t="s">
+      <c r="K59" s="10"/>
+      <c r="L59" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="14"/>
-      <c r="S59" s="14"/>
-      <c r="T59" s="14"/>
-      <c r="U59" s="14"/>
-      <c r="V59" s="14"/>
-      <c r="W59" s="5"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="11"/>
+      <c r="S59" s="11"/>
+      <c r="T59" s="11"/>
+      <c r="U59" s="11"/>
+      <c r="V59" s="11"/>
+      <c r="W59" s="2"/>
     </row>
     <row r="60" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K60" s="15"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="8"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="7"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="4"/>
     </row>
     <row r="61" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K61" s="15"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="7"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="11"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="11"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="12"/>
-      <c r="W61" s="7"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="6"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="4"/>
     </row>
     <row r="62" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K62" s="15"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="7"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="4"/>
     </row>
     <row r="63" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K63" s="15"/>
-      <c r="L63" s="6" t="s">
+      <c r="K63" s="12"/>
+      <c r="L63" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="15"/>
-      <c r="R63" s="13"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="15"/>
-      <c r="U63" s="13"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="7"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="11"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="11"/>
+      <c r="T63" s="12"/>
+      <c r="U63" s="10"/>
+      <c r="V63" s="11"/>
+      <c r="W63" s="4"/>
     </row>
     <row r="64" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K64" s="15"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="12"/>
-      <c r="O64" s="15"/>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="9"/>
-      <c r="R64" s="15"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="15"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="7"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="12"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="12"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="4"/>
     </row>
     <row r="65" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K65" s="15"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
-      <c r="T65" s="6"/>
-      <c r="U65" s="6"/>
-      <c r="V65" s="6"/>
-      <c r="W65" s="7"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="4"/>
     </row>
     <row r="66" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K66" s="9"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-      <c r="O66" s="12"/>
-      <c r="P66" s="12"/>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="12"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-      <c r="U66" s="12"/>
-      <c r="V66" s="12"/>
-      <c r="W66" s="10"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="R66" s="9"/>
+      <c r="S66" s="9"/>
+      <c r="T66" s="9"/>
+      <c r="U66" s="9"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="7"/>
     </row>
     <row r="67" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K67" s="24" t="s">
+      <c r="K67" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
-      <c r="Q67" s="14"/>
-      <c r="R67" s="14"/>
-      <c r="S67" s="14"/>
-      <c r="T67" s="14"/>
-      <c r="U67" s="14"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="5"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="11"/>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="11"/>
+      <c r="T67" s="11"/>
+      <c r="U67" s="11"/>
+      <c r="V67" s="11"/>
+      <c r="W67" s="2"/>
     </row>
     <row r="68" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K68" s="25"/>
-      <c r="L68" s="6" t="s">
+      <c r="K68" s="21"/>
+      <c r="L68" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M68" s="6"/>
-      <c r="N68" s="6"/>
-      <c r="O68" s="6"/>
-      <c r="P68" s="6"/>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
-      <c r="V68" s="6"/>
-      <c r="W68" s="7"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="4"/>
     </row>
     <row r="69" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K69" s="25"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="7"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="4"/>
     </row>
     <row r="70" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K70" s="25"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="7"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="4"/>
     </row>
     <row r="71" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K71" s="25"/>
-      <c r="L71" s="6" t="s">
+      <c r="K71" s="21"/>
+      <c r="L71" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M71" s="6"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="6"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="6"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="7"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="4"/>
     </row>
     <row r="72" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K72" s="25"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
-      <c r="V72" s="6"/>
-      <c r="W72" s="7"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="4"/>
     </row>
     <row r="73" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K73" s="25"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="6"/>
-      <c r="S73" s="6"/>
-      <c r="T73" s="6"/>
-      <c r="U73" s="6"/>
-      <c r="V73" s="6"/>
-      <c r="W73" s="7"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="4"/>
     </row>
     <row r="74" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K74" s="25"/>
-      <c r="L74" s="6" t="s">
+      <c r="K74" s="21"/>
+      <c r="L74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M74" s="6"/>
-      <c r="N74" s="6"/>
-      <c r="O74" s="6"/>
-      <c r="P74" s="6"/>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
-      <c r="V74" s="6"/>
-      <c r="W74" s="7"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="4"/>
     </row>
     <row r="75" spans="11:23" x14ac:dyDescent="0.25">
-      <c r="K75" s="26"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12"/>
-      <c r="O75" s="12"/>
-      <c r="P75" s="12"/>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="12"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12"/>
-      <c r="U75" s="12"/>
-      <c r="V75" s="12"/>
-      <c r="W75" s="10"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="9"/>
+      <c r="O75" s="9"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4713,4 +4723,28 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538F44AC-C3BD-4D64-A281-6207507509E4}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" display="https://blog.csdn.net/qq_42078934/article/details/126888338" xr:uid="{57BED0AD-37C7-4BAB-A8BD-5D1FC0A15C0E}"/>
+    <hyperlink ref="A2" r:id="rId2" display="https://www.bilibili.com/video/BV1PksxeqEQr/" xr:uid="{773A9C0D-727A-47DA-AC35-A663E32E9BC5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>